--- a/output/pdf_financials_xlsx/NKL.xlsx
+++ b/output/pdf_financials_xlsx/NKL.xlsx
@@ -3368,25 +3368,25 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.103456</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.383513</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>1.071486</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>1.586347</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>1.494836</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.705913</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.834732</v>
       </c>
     </row>
     <row r="93">
@@ -5624,7 +5624,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E21" s="5" t="n">
         <v>0.103456</v>
       </c>

--- a/output/pdf_financials_xlsx/NKL.xlsx
+++ b/output/pdf_financials_xlsx/NKL.xlsx
@@ -1734,7 +1734,7 @@
         <v>8.057729999999999</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>9.084694000000001</v>
       </c>
     </row>
     <row r="35">
@@ -1790,7 +1790,7 @@
         <v>8.104454</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>9.084694000000001</v>
       </c>
     </row>
     <row r="37">
@@ -2126,7 +2126,7 @@
         <v>1.632251</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>11.572571</v>
+        <v>2.487877</v>
       </c>
     </row>
     <row r="49">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">

--- a/output/pdf_financials_xlsx/NKL.xlsx
+++ b/output/pdf_financials_xlsx/NKL.xlsx
@@ -3994,7 +3994,7 @@
         <v>0</v>
       </c>
       <c r="C115" s="3" t="n">
-        <v>0</v>
+        <v>5.179892</v>
       </c>
       <c r="D115" s="3" t="n">
         <v>0</v>
@@ -4006,7 +4006,7 @@
         <v>0</v>
       </c>
       <c r="G115" s="3" t="n">
-        <v>0</v>
+        <v>0.014591</v>
       </c>
       <c r="H115" s="3" t="n">
         <v>0</v>
@@ -4173,10 +4173,10 @@
         <v>0</v>
       </c>
       <c r="D121" s="3" t="n">
-        <v>0</v>
+        <v>-0.383556</v>
       </c>
       <c r="E121" s="3" t="n">
-        <v>0</v>
+        <v>-0.85046</v>
       </c>
       <c r="F121" s="3" t="n">
         <v>0</v>
@@ -13748,7 +13748,11 @@
           <t>Proceeds from the sale of marketable securities</t>
         </is>
       </c>
-      <c r="D187" t="inlineStr"/>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E187" t="inlineStr">
         <is>
           <t>-</t>
@@ -14346,7 +14350,11 @@
           <t>Deferred tax expense</t>
         </is>
       </c>
-      <c r="D199" t="inlineStr"/>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E199" t="inlineStr">
         <is>
           <t>-</t>
@@ -14481,7 +14489,11 @@
           <t>Common shares issued for cash</t>
         </is>
       </c>
-      <c r="D202" t="inlineStr"/>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E202" t="inlineStr">
         <is>
           <t>-</t>
@@ -15120,7 +15132,11 @@
           <t>Repurchase of shares</t>
         </is>
       </c>
-      <c r="D215" t="inlineStr"/>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>RepurchaseOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E215" t="inlineStr">
         <is>
           <t>-</t>
@@ -16116,7 +16132,11 @@
           <t>Proceeds from the sale of marketable securities (Note 7)</t>
         </is>
       </c>
-      <c r="D235" t="inlineStr"/>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E235" t="inlineStr">
         <is>
           <t>-</t>
@@ -16167,7 +16187,11 @@
           <t>Common shares issued for cash (Note 12(b))</t>
         </is>
       </c>
-      <c r="D236" t="inlineStr"/>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E236" t="inlineStr">
         <is>
           <t>-</t>
@@ -16518,7 +16542,11 @@
           <t>Proceeds from the sale of marketable securities (Note 8)</t>
         </is>
       </c>
-      <c r="D243" t="inlineStr"/>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E243" t="inlineStr">
         <is>
           <t>-</t>
